--- a/survey_templates/050_sewing_machine_parts_quiz--survey_templates.xlsx
+++ b/survey_templates/050_sewing_machine_parts_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sewing_machine_parts_quiz</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_is_a_sewing_machine</t>
+          <t>What is a sewing machine used for?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sewing_machine_parts_quiz</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>parts_of_a_sewing_machine</t>
+          <t>Basic parts of a sewing machine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part</t>
+          <t>Correct part used for a specific function</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sewing_machine_part</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>incorrect_sewing_machine_part</t>
+          <t>Parts used for a specific function</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sewing_machine_part_quiz_question</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_is_a_sewing_machine_used_for</t>
+          <t>Correct sewing machine used for</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part_quiz</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_is_a_sewing_machine_used_for</t>
+          <t>Question 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parts_of_a_sewing_machine_quiz_question</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_parts_are_used_in_a_sewing_machine</t>
+          <t>Correct sewing machine used for a specific task</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,407 +681,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what_parts_used_in_a_sewing_machine</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_parts_used_in_a_sewing_machine</t>
+          <t>Parts used for a specific task</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_used_for</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>correct_parts_used_in_a_sewing_machine</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>wrong_sewing_machine_used_for</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>incorrect_parts_used_in_a_sewing_machine</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>correct_quiz_question</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_used_for</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_part_quiz_question</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_part</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_used_for</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_part_quiz</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_part</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>parts_of_a_sewing_machine_quiz_question</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>parts_of_a_sewing_machine_quiz</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>correct_parts_used_in_a_sewing_machine</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>correct_parts_used_in_a_sewing_machine</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>what_parts_used_in_a_sewing_machine_quiz</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>what_parts_used_in_a_sewing_machine_quiz</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>correct_parts_used_in_a_sewing_machine_quiz</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>correct_parts_used_in_a_sewing_machine_quiz</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>incorrect_parts_used_in_a_sewing_machine_quiz</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>incorrect_parts_used_in_a_sewing_machine_quiz</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_quiz_question</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_quiz_question</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_part_quiz_question</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_part_quiz_question</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>what_is_a_sewing_machine_used_for_quiz</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,646 +735,578 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sewing_machine_parts_quiz_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sewing,_embroidery,_and_other_crafts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>sewing, embroidery, and other crafts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sewing_machine_parts_quiz_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>quilting_and_sewing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>quilting and sewing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tailoring_and_embroidery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>tailoring and embroidery</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bobbin_winder</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sewing_machine_part_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>spare_bobbin_holder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Spare bobbin holder</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sewing_machine_part_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bobbin_case</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bobbin case</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part_quiz_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sewing_machine_needle</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sewing machine needle</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part_quiz_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>thread_guides</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Thread guides</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>parts_of_a_sewing_machine_quiz_question_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>liner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Liner</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>parts_of_a_sewing_machine_quiz_question_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>presser_foot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Presser foot</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>what_parts_used_in_a_sewing_machine_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>take-up_lever</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Take-up lever</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>what_parts_used_in_a_sewing_machine_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sewing_machine_presser</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sewing machine presser</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_used_for_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bobbin_winder</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_used_for_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>spare_bobbin_holder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Spare bobbin holder</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wrong_sewing_machine_used_for_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bobbin_case</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bobbin case</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wrong_sewing_machine_used_for_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sewing_machine_needle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sewing machine needle</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>correct_quiz_question_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bobbin_winder</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>correct_quiz_question_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>spare_bobbin_holder</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Spare bobbin holder</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part_quiz_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bobbin_case</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bobbin case</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_part_quiz_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sewing_machine_needle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sewing machine needle</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>parts_of_a_sewing_machine_quiz_question_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sewing_machine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sewing machine</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>parts_of_a_sewing_machine_quiz_question_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>overlock_machine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Overlock machine</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>correct_parts_used_in_a_sewing_machine_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>quilter's_machine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Quilter's machine</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>correct_parts_used_in_a_sewing_machine_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bobbin_winder</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>what_is_a_sewing_machine_used_for_quiz_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>spare_bobbin_holder</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Spare bobbin holder</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>what_is_a_sewing_machine_used_for_quiz_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bobbin_case</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bobbin case</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_used_for_quiz_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sewing_machine_needle</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sewing machine needle</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_used_for_quiz_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sewing_machine</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sewing machine</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>what_parts_used_in_a_sewing_machine_quiz_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>overlock_machine</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Overlock machine</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>what_parts_used_in_a_sewing_machine_quiz_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>quilter's_machine</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Quilter's machine</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>correct_parts_used_in_a_sewing_machine_quiz_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bobbin_winder</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bobbin winder</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>correct_parts_used_in_a_sewing_machine_quiz_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>spare_bobbin_holder</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Spare bobbin holder</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_used_for_quiz_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bobbin_case</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bobbin case</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>correct_sewing_machine_used_for_quiz_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sewing_machine_needle</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>incorrect_parts_used_in_a_sewing_machine_quiz_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>incorrect_parts_used_in_a_sewing_machine_quiz_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_quiz_question_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>correct_sewing_machine_quiz_question_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Sewing machine needle</t>
         </is>
       </c>
     </row>
